--- a/Example/demo-os.xlsx
+++ b/Example/demo-os.xlsx
@@ -523,7 +523,7 @@
         <v>POLO-01</v>
       </c>
       <c r="G5" t="str">
-        <v>F0001</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -575,7 +575,7 @@
         <v>POLO-01</v>
       </c>
       <c r="G7" t="str">
-        <v>F0001</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -627,7 +627,7 @@
         <v>POLO-01</v>
       </c>
       <c r="G9" t="str">
-        <v>F0001</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v/>

--- a/Example/demo-os.xlsx
+++ b/Example/demo-os.xlsx
@@ -439,7 +439,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E2" t="str">
-        <v>LigacaoAgua</v>
+        <v>RedeRamalAgua</v>
       </c>
       <c r="F2" t="str">
         <v>POLO-01</v>
@@ -465,7 +465,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E3" t="str">
-        <v>Vistoria</v>
+        <v>Outros</v>
       </c>
       <c r="F3" t="str">
         <v>POLO-01</v>
@@ -491,7 +491,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E4" t="str">
-        <v>ReparoRede</v>
+        <v>RedeRamalEsgoto</v>
       </c>
       <c r="F4" t="str">
         <v>POLO-01</v>
@@ -517,7 +517,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E5" t="str">
-        <v>TrocaHidrometro</v>
+        <v>CavaleteHidrometro</v>
       </c>
       <c r="F5" t="str">
         <v>POLO-01</v>
@@ -543,7 +543,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E6" t="str">
-        <v>ReligacaoAgua</v>
+        <v>Desobstrucao</v>
       </c>
       <c r="F6" t="str">
         <v>POLO-01</v>
@@ -569,7 +569,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E7" t="str">
-        <v>CorteAgua</v>
+        <v>CavaleteHidrometro</v>
       </c>
       <c r="F7" t="str">
         <v>POLO-01</v>
@@ -595,7 +595,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E8" t="str">
-        <v>Outros</v>
+        <v>ReposicaoPiso</v>
       </c>
       <c r="F8" t="str">
         <v>POLO-01</v>
@@ -621,7 +621,7 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E9" t="str">
-        <v>Vistoria</v>
+        <v>ReposicaoAsfaltica</v>
       </c>
       <c r="F9" t="str">
         <v>POLO-01</v>

--- a/Example/demo-os.xlsx
+++ b/Example/demo-os.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,15 +413,18 @@
         <v>cidade</v>
       </c>
       <c r="E1" t="str">
+        <v>codigo_tss</v>
+      </c>
+      <c r="F1" t="str">
         <v>tipo_servico</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>polo</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>fiscal</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>observacao</v>
       </c>
     </row>
@@ -439,15 +442,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E2" t="str">
-        <v>RedeRamalAgua</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="str">
-        <v>POLO-01</v>
+        <v>RedeAgua</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>OS demo sem fiscal para testar atribuicao.</v>
       </c>
     </row>
@@ -465,15 +471,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E3" t="str">
-        <v>Outros</v>
+        <v>2860</v>
       </c>
       <c r="F3" t="str">
-        <v>POLO-01</v>
+        <v>RamalAgua</v>
       </c>
       <c r="G3" t="str">
+        <v>POLO-01</v>
+      </c>
+      <c r="H3" t="str">
         <v>F0001</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>OS demo atribuida para testar tabulacao.</v>
       </c>
     </row>
@@ -491,15 +500,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E4" t="str">
+        <v>5880</v>
+      </c>
+      <c r="F4" t="str">
         <v>RedeRamalEsgoto</v>
       </c>
-      <c r="F4" t="str">
-        <v>POLO-01</v>
-      </c>
       <c r="G4" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v/>
       </c>
     </row>
@@ -517,15 +529,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E5" t="str">
+        <v>2010</v>
+      </c>
+      <c r="F5" t="str">
         <v>CavaleteHidrometro</v>
       </c>
-      <c r="F5" t="str">
-        <v>POLO-01</v>
-      </c>
       <c r="G5" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v/>
       </c>
     </row>
@@ -543,15 +558,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E6" t="str">
+        <v>5810</v>
+      </c>
+      <c r="F6" t="str">
         <v>Desobstrucao</v>
       </c>
-      <c r="F6" t="str">
-        <v>POLO-01</v>
-      </c>
       <c r="G6" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v/>
       </c>
     </row>
@@ -569,15 +587,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E7" t="str">
-        <v>CavaleteHidrometro</v>
+        <v>7070</v>
       </c>
       <c r="F7" t="str">
-        <v>POLO-01</v>
+        <v>LavagemEee</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v/>
       </c>
     </row>
@@ -595,15 +616,18 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E8" t="str">
+        <v>7670</v>
+      </c>
+      <c r="F8" t="str">
         <v>ReposicaoPiso</v>
       </c>
-      <c r="F8" t="str">
-        <v>POLO-01</v>
-      </c>
       <c r="G8" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v/>
       </c>
     </row>
@@ -621,21 +645,24 @@
         <v>Cidade Teste</v>
       </c>
       <c r="E9" t="str">
+        <v>7850</v>
+      </c>
+      <c r="F9" t="str">
         <v>ReposicaoAsfaltica</v>
       </c>
-      <c r="F9" t="str">
-        <v>POLO-01</v>
-      </c>
       <c r="G9" t="str">
-        <v/>
+        <v>POLO-01</v>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>